--- a/data/2-master_reddit_links_curated.xlsx
+++ b/data/2-master_reddit_links_curated.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\RedditBoardApplication\RedditBoardV3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E67B2F3-9DAC-4212-ABBE-42E79218D2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EA6F10-E8C3-4DE5-A196-3B33E23BBEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="238" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="DeletedContents" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$U$102</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="832">
   <si>
     <t>reddit_id</t>
   </si>
@@ -2342,9 +2343,6 @@
     <t>coordinatedscalypachyderm</t>
   </si>
   <si>
-    <t>YUser_Maintainence_Merged</t>
-  </si>
-  <si>
     <t>niftyunhappyflickertailsquirrel</t>
   </si>
   <si>
@@ -2495,13 +2493,49 @@
     <t>YUser_BeltLoops.md</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>NotApplicable</t>
   </si>
   <si>
     <t>ALREADY DOWNLOADED</t>
+  </si>
+  <si>
+    <t>ZUser_Maintainence_Merged</t>
+  </si>
+  <si>
+    <t>He is my bitch.</t>
+  </si>
+  <si>
+    <t>chastity,permachastity,chastity inverted,humilliation</t>
+  </si>
+  <si>
+    <t>post asking how to shrink dick</t>
+  </si>
+  <si>
+    <t>YUser_ShrinkPill.md</t>
+  </si>
+  <si>
+    <t>https://old.reddit.com/r/ChastityCouples/comments/1p3ouyf/it_will_stay_closed_as_long_as_i_have_my_period</t>
+  </si>
+  <si>
+    <t>https://old.reddit.com/r/chastity/comments/1k876oh/how_can_i_make_his_sissy_cock_not_get_hard_and/mp4m9l7</t>
+  </si>
+  <si>
+    <t>https://i.redd.it/nq39etcczr2g1.gif</t>
+  </si>
+  <si>
+    <t>couple_8890_</t>
+  </si>
+  <si>
+    <t>It will stay closed as long as I have my period! Right? 😈</t>
+  </si>
+  <si>
+    <t>chastity,chastity put on</t>
+  </si>
+  <si>
+    <t>good quality chastity put on</t>
+  </si>
+  <si>
+    <t>nq39etcczr2g1.gif</t>
   </si>
 </sst>
 </file>
@@ -2587,7 +2621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2596,11 +2630,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FFFF00FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF00FF"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color auto="1"/>
@@ -2623,8 +2670,13 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF00FF"/>
+        <color auto="1"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2907,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:U195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
@@ -3022,13 +3074,13 @@
         <v>303</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>502</v>
@@ -3052,10 +3104,10 @@
         <v>498</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T2" s="2" t="str">
         <f>IF(ISBLANK(N2)=TRUE,"Pending","Done")</f>
@@ -3088,13 +3140,13 @@
         <v>490</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>505</v>
@@ -3121,7 +3173,7 @@
         <v>755</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T3" s="2" t="str">
         <f>IF(ISBLANK(N3)=TRUE,"Pending","Done")</f>
@@ -3154,7 +3206,7 @@
         <v>66</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>65</v>
@@ -3187,7 +3239,7 @@
         <v>756</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T4" s="2" t="str">
         <f>IF(ISBLANK(N4)=TRUE,"Pending","Done")</f>
@@ -3220,13 +3272,13 @@
         <v>471</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>505</v>
@@ -3253,7 +3305,7 @@
         <v>754</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T5" s="2" t="str">
         <f>IF(ISBLANK(N5)=TRUE,"Pending","Done")</f>
@@ -3286,13 +3338,13 @@
         <v>481</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>505</v>
@@ -3319,7 +3371,7 @@
         <v>753</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T6" s="2" t="str">
         <f>IF(ISBLANK(N6)=TRUE,"Pending","Done")</f>
@@ -3352,13 +3404,13 @@
         <v>441</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>505</v>
@@ -3367,7 +3419,7 @@
         <v>549</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>501</v>
@@ -3385,7 +3437,7 @@
         <v>746</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T7" s="2" t="str">
         <f>IF(ISBLANK(N7)=TRUE,"Pending","Done")</f>
@@ -3418,7 +3470,7 @@
         <v>389</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>367</v>
@@ -3448,10 +3500,10 @@
         <v>498</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T8" s="2" t="str">
         <f>IF(ISBLANK(N8)=TRUE,"Pending","Done")</f>
@@ -3484,13 +3536,13 @@
         <v>218</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>505</v>
@@ -3517,7 +3569,7 @@
         <v>714</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T9" s="2" t="str">
         <f>IF(ISBLANK(N9)=TRUE,"Pending","Done")</f>
@@ -3548,7 +3600,7 @@
         <v>429</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>367</v>
@@ -3578,10 +3630,10 @@
         <v>498</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T10" s="2" t="str">
         <f>IF(ISBLANK(N10)=TRUE,"Pending","Done")</f>
@@ -3614,13 +3666,13 @@
         <v>347</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>506</v>
@@ -3647,14 +3699,14 @@
         <v>747</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T11" s="2" t="str">
         <f>IF(ISBLANK(N11)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U11" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="60" x14ac:dyDescent="0.25">
@@ -3680,13 +3732,13 @@
         <v>476</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>505</v>
@@ -3713,7 +3765,7 @@
         <v>716</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T12" s="2" t="str">
         <f>IF(ISBLANK(N12)=TRUE,"Pending","Done")</f>
@@ -3746,7 +3798,7 @@
         <v>331</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>330</v>
@@ -3776,10 +3828,10 @@
         <v>498</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T13" s="2" t="str">
         <f>IF(ISBLANK(N13)=TRUE,"Pending","Done")</f>
@@ -3812,22 +3864,22 @@
         <v>37</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>505</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>501</v>
@@ -3836,16 +3888,16 @@
         <v>6</v>
       </c>
       <c r="P14" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R14" s="2" t="s">
         <v>813</v>
       </c>
-      <c r="Q14" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>814</v>
-      </c>
       <c r="S14" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T14" s="2" t="str">
         <f>IF(ISBLANK(N14)=TRUE,"Pending","Done")</f>
@@ -3878,7 +3930,7 @@
         <v>145</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>99</v>
@@ -3911,7 +3963,7 @@
         <v>724</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T15" s="2" t="str">
         <f>IF(ISBLANK(N15)=TRUE,"Pending","Done")</f>
@@ -3944,22 +3996,22 @@
         <v>31</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>505</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>501</v>
@@ -3968,16 +4020,16 @@
         <v>4</v>
       </c>
       <c r="P16" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>816</v>
       </c>
-      <c r="Q16" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>817</v>
-      </c>
       <c r="S16" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T16" s="2" t="str">
         <f>IF(ISBLANK(N16)=TRUE,"Pending","Done")</f>
@@ -4010,19 +4062,19 @@
         <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>502</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>599</v>
@@ -4034,16 +4086,16 @@
         <v>3</v>
       </c>
       <c r="P17" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R17" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="Q17" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>804</v>
-      </c>
       <c r="S17" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T17" s="2" t="str">
         <f>IF(ISBLANK(N17)=TRUE,"Pending","Done")</f>
@@ -4076,7 +4128,7 @@
         <v>161</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>99</v>
@@ -4109,7 +4161,7 @@
         <v>728</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T18" s="2" t="str">
         <f>IF(ISBLANK(N18)=TRUE,"Pending","Done")</f>
@@ -4142,13 +4194,13 @@
         <v>285</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>503</v>
@@ -4175,7 +4227,7 @@
         <v>704</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T19" s="2" t="str">
         <f>IF(ISBLANK(N19)=TRUE,"Pending","Done")</f>
@@ -4208,7 +4260,7 @@
         <v>486</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>485</v>
@@ -4241,7 +4293,7 @@
         <v>751</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T20" s="2" t="str">
         <f>IF(ISBLANK(N20)=TRUE,"Pending","Done")</f>
@@ -4274,7 +4326,7 @@
         <v>137</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>99</v>
@@ -4304,10 +4356,10 @@
         <v>498</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T21" s="2" t="str">
         <f>IF(ISBLANK(N21)=TRUE,"Pending","Done")</f>
@@ -4340,7 +4392,7 @@
         <v>197</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>99</v>
@@ -4373,7 +4425,7 @@
         <v>738</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T22" s="2" t="str">
         <f>IF(ISBLANK(N22)=TRUE,"Pending","Done")</f>
@@ -4404,13 +4456,13 @@
         <v>416</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>503</v>
@@ -4434,10 +4486,10 @@
         <v>498</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T23" s="2" t="str">
         <f>IF(ISBLANK(N23)=TRUE,"Pending","Done")</f>
@@ -4470,7 +4522,7 @@
         <v>177</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>99</v>
@@ -4503,7 +4555,7 @@
         <v>732</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T24" s="2" t="str">
         <f>IF(ISBLANK(N24)=TRUE,"Pending","Done")</f>
@@ -4539,10 +4591,10 @@
         <v>178</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>505</v>
@@ -4551,7 +4603,7 @@
         <v>536</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>501</v>
@@ -4569,14 +4621,14 @@
         <v>733</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T25" s="2" t="str">
         <f>IF(ISBLANK(N25)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="75" x14ac:dyDescent="0.25">
@@ -4602,7 +4654,7 @@
         <v>425</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>367</v>
@@ -4635,7 +4687,7 @@
         <v>703</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T26" s="2" t="str">
         <f>IF(ISBLANK(N26)=TRUE,"Pending","Done")</f>
@@ -4683,7 +4735,7 @@
         <v>556</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>501</v>
@@ -4701,7 +4753,7 @@
         <v>750</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T27" s="2" t="str">
         <f>IF(ISBLANK(N27)=TRUE,"Pending","Done")</f>
@@ -4734,7 +4786,7 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>76</v>
@@ -4749,7 +4801,7 @@
         <v>555</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>501</v>
@@ -4767,7 +4819,7 @@
         <v>750</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T28" s="2" t="str">
         <f>IF(ISBLANK(N28)=TRUE,"Pending","Done")</f>
@@ -4800,7 +4852,7 @@
         <v>435</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>434</v>
@@ -4830,10 +4882,10 @@
         <v>498</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T29" s="2" t="str">
         <f>IF(ISBLANK(N29)=TRUE,"Pending","Done")</f>
@@ -4866,7 +4918,7 @@
         <v>201</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I30" s="3" t="s">
         <v>99</v>
@@ -4899,7 +4951,7 @@
         <v>739</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T30" s="2" t="str">
         <f>IF(ISBLANK(N30)=TRUE,"Pending","Done")</f>
@@ -4932,7 +4984,7 @@
         <v>112</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I31" s="3" t="s">
         <v>99</v>
@@ -4965,7 +5017,7 @@
         <v>723</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T31" s="2" t="str">
         <f>IF(ISBLANK(N31)=TRUE,"Pending","Done")</f>
@@ -4998,7 +5050,7 @@
         <v>205</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>99</v>
@@ -5028,10 +5080,10 @@
         <v>498</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T32" s="2" t="str">
         <f>IF(ISBLANK(N32)=TRUE,"Pending","Done")</f>
@@ -5064,7 +5116,7 @@
         <v>133</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>99</v>
@@ -5097,7 +5149,7 @@
         <v>721</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T33" s="2" t="str">
         <f>IF(ISBLANK(N33)=TRUE,"Pending","Done")</f>
@@ -5130,7 +5182,7 @@
         <v>165</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>99</v>
@@ -5163,7 +5215,7 @@
         <v>729</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T34" s="2" t="str">
         <f>IF(ISBLANK(N34)=TRUE,"Pending","Done")</f>
@@ -5173,54 +5225,54 @@
         <v>499</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="300" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>457</v>
+        <v>818</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O35" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>498</v>
@@ -5229,7 +5281,7 @@
         <v>749</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T35" s="2" t="str">
         <f>IF(ISBLANK(N35)=TRUE,"Pending","Done")</f>
@@ -5239,15 +5291,15 @@
         <v>499</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="240" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="300" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>449</v>
@@ -5256,37 +5308,37 @@
         <v>451</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O36" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>498</v>
@@ -5295,7 +5347,7 @@
         <v>749</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T36" s="2" t="str">
         <f>IF(ISBLANK(N36)=TRUE,"Pending","Done")</f>
@@ -5305,54 +5357,54 @@
         <v>499</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="240" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>451</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>453</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>820</v>
+        <v>461</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O37" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>498</v>
@@ -5361,7 +5413,7 @@
         <v>749</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T37" s="2" t="str">
         <f>IF(ISBLANK(N37)=TRUE,"Pending","Done")</f>
@@ -5394,7 +5446,7 @@
         <v>185</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>99</v>
@@ -5427,7 +5479,7 @@
         <v>734</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T38" s="2" t="str">
         <f>IF(ISBLANK(N38)=TRUE,"Pending","Done")</f>
@@ -5460,13 +5512,13 @@
         <v>319</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K39" s="3" t="s">
         <v>505</v>
@@ -5490,10 +5542,10 @@
         <v>498</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T39" s="2" t="str">
         <f>IF(ISBLANK(N39)=TRUE,"Pending","Done")</f>
@@ -5526,13 +5578,13 @@
         <v>378</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>505</v>
@@ -5559,7 +5611,7 @@
         <v>711</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T40" s="2" t="str">
         <f>IF(ISBLANK(N40)=TRUE,"Pending","Done")</f>
@@ -5569,63 +5621,61 @@
         <v>499</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>369</v>
-      </c>
+    <row r="41" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+      <c r="A41" s="2"/>
       <c r="B41" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>370</v>
+        <v>825</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>528</v>
+        <v>821</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>602</v>
+        <v>817</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O41" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>632</v>
+        <v>822</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>725</v>
+        <v>823</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T41" s="2" t="str">
         <f>IF(ISBLANK(N41)=TRUE,"Pending","Done")</f>
@@ -5635,63 +5685,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>351</v>
+        <v>98</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>799</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>580</v>
+        <v>528</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O42" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>686</v>
+        <v>632</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>773</v>
+        <v>725</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T42" s="2" t="str">
         <f>IF(ISBLANK(N42)=TRUE,"Pending","Done")</f>
@@ -5701,111 +5751,111 @@
         <v>499</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="105" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>253</v>
+        <v>348</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>254</v>
+        <v>349</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>85</v>
+        <v>351</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>248</v>
+        <v>352</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>248</v>
+        <v>798</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>248</v>
+        <v>794</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>819</v>
+        <v>606</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O43" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>668</v>
+        <v>686</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T43" s="2" t="str">
         <f>IF(ISBLANK(N43)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>238</v>
+        <v>85</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>800</v>
+        <v>248</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>800</v>
+        <v>248</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>501</v>
@@ -5814,16 +5864,16 @@
         <v>7</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T44" s="2" t="str">
         <f>IF(ISBLANK(N44)=TRUE,"Pending","Done")</f>
@@ -5833,63 +5883,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="105" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>462</v>
+        <v>235</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>463</v>
+        <v>236</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>464</v>
+        <v>237</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>451</v>
+        <v>238</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>465</v>
+        <v>239</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>466</v>
+        <v>240</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>551</v>
+        <v>573</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>598</v>
+        <v>817</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O45" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>654</v>
+        <v>677</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>748</v>
+        <v>764</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T45" s="2" t="str">
         <f>IF(ISBLANK(N45)=TRUE,"Pending","Done")</f>
@@ -5899,195 +5949,195 @@
         <v>499</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>18</v>
+        <v>462</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>21</v>
+        <v>464</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>22</v>
+        <v>451</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>23</v>
+        <v>465</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>24</v>
+        <v>466</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>800</v>
+        <v>817</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>799</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="K46" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>806</v>
+      <c r="L46" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="O46" s="2">
-        <v>7</v>
-      </c>
-      <c r="P46" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>819</v>
+      <c r="O46" s="3">
+        <v>8</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="T46" s="2" t="str">
         <f>IF(ISBLANK(N46)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
-      <c r="U46" s="2" t="s">
+      <c r="U46" s="3" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>267</v>
+        <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>269</v>
+        <v>21</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>270</v>
+        <v>23</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>271</v>
+        <v>24</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>800</v>
+        <v>817</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="K47" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K47" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>819</v>
+      <c r="L47" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="O47" s="3">
-        <v>6</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>819</v>
+      <c r="O47" s="2">
+        <v>7</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="T47" s="2" t="str">
         <f>IF(ISBLANK(N47)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
-      <c r="U47" s="3" t="s">
+      <c r="U47" s="2" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>267</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>268</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>269</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>61</v>
+        <v>271</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>512</v>
+        <v>568</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>600</v>
+        <v>817</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>708</v>
+        <v>761</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T48" s="2" t="str">
         <f>IF(ISBLANK(N48)=TRUE,"Pending","Done")</f>
@@ -6097,63 +6147,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>332</v>
+        <v>56</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>333</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>334</v>
+        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>335</v>
+        <v>59</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>324</v>
+        <v>60</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>336</v>
+        <v>61</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>324</v>
+        <v>799</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>324</v>
+        <v>799</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O49" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T49" s="2" t="str">
         <f>IF(ISBLANK(N49)=TRUE,"Pending","Done")</f>
@@ -6163,45 +6213,45 @@
         <v>499</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>390</v>
+        <v>332</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>391</v>
+        <v>333</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>392</v>
+        <v>334</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>98</v>
+        <v>335</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>394</v>
+        <v>336</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>393</v>
+        <v>324</v>
       </c>
       <c r="K50" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>501</v>
@@ -6210,16 +6260,16 @@
         <v>8</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T50" s="2" t="str">
         <f>IF(ISBLANK(N50)=TRUE,"Pending","Done")</f>
@@ -6229,42 +6279,42 @@
         <v>499</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>408</v>
+        <v>390</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K51" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>601</v>
@@ -6273,19 +6323,19 @@
         <v>501</v>
       </c>
       <c r="O51" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="T51" s="2" t="str">
         <f>IF(ISBLANK(N51)=TRUE,"Pending","Done")</f>
@@ -6295,42 +6345,42 @@
         <v>499</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>601</v>
@@ -6339,19 +6389,19 @@
         <v>501</v>
       </c>
       <c r="O52" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T52" s="2" t="str">
         <f>IF(ISBLANK(N52)=TRUE,"Pending","Done")</f>
@@ -6361,63 +6411,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>323</v>
+        <v>98</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>325</v>
+        <v>403</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>558</v>
+        <v>518</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O53" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>661</v>
+        <v>622</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>752</v>
+        <v>715</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T53" s="2" t="str">
         <f>IF(ISBLANK(N53)=TRUE,"Pending","Done")</f>
@@ -6429,59 +6479,61 @@
     </row>
     <row r="54" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D54" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>322</v>
+      </c>
       <c r="E54" s="2" t="s">
-        <v>29</v>
+        <v>323</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>800</v>
+        <v>324</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>800</v>
+        <v>324</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O54" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T54" s="2" t="str">
         <f>IF(ISBLANK(N54)=TRUE,"Pending","Done")</f>
@@ -6491,129 +6543,127 @@
         <v>499</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>50</v>
+        <v>310</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>52</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="D55" s="2"/>
       <c r="E55" s="2" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>55</v>
+        <v>313</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O55" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>766</v>
+        <v>819</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="T55" s="2" t="str">
         <f>IF(ISBLANK(N55)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="120" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>245</v>
+        <v>50</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>246</v>
+        <v>51</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>247</v>
+        <v>52</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>85</v>
+        <v>53</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>248</v>
+        <v>799</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>248</v>
+        <v>799</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O56" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P56" s="3" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T56" s="2" t="str">
         <f>IF(ISBLANK(N56)=TRUE,"Pending","Done")</f>
@@ -6623,18 +6673,18 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="225" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="120" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>85</v>
@@ -6646,7 +6696,7 @@
         <v>249</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>252</v>
+        <v>818</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>248</v>
@@ -6658,10 +6708,10 @@
         <v>505</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>501</v>
@@ -6670,7 +6720,7 @@
         <v>4</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>498</v>
@@ -6679,7 +6729,7 @@
         <v>763</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T57" s="2" t="str">
         <f>IF(ISBLANK(N57)=TRUE,"Pending","Done")</f>
@@ -6689,63 +6739,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="225" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>171</v>
+        <v>251</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>172</v>
+        <v>246</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>99</v>
+        <v>248</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>819</v>
+        <v>252</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>99</v>
+        <v>248</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>99</v>
+        <v>248</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>602</v>
+        <v>817</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O58" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>638</v>
+        <v>676</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T58" s="2" t="str">
         <f>IF(ISBLANK(N58)=TRUE,"Pending","Done")</f>
@@ -6755,63 +6805,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>95</v>
+        <v>379</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>96</v>
+        <v>824</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>97</v>
+        <v>826</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>99</v>
+        <v>827</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>100</v>
+        <v>828</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>99</v>
+        <v>817</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>601</v>
+      <c r="L59" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>599</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O59" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>646</v>
+        <v>830</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>741</v>
+        <v>831</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T59" s="2" t="str">
         <f>IF(ISBLANK(N59)=TRUE,"Pending","Done")</f>
@@ -6821,63 +6871,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>101</v>
+        <v>170</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>104</v>
+        <v>817</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O60" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P60" s="3" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T60" s="2" t="str">
         <f>IF(ISBLANK(N60)=TRUE,"Pending","Done")</f>
@@ -6887,63 +6937,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>516</v>
+        <v>544</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O61" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P61" s="3" t="s">
-        <v>620</v>
+        <v>646</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>713</v>
+        <v>741</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T61" s="2" t="str">
         <f>IF(ISBLANK(N61)=TRUE,"Pending","Done")</f>
@@ -6953,63 +7003,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>98</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>213</v>
+        <v>100</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>819</v>
+        <v>104</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>602</v>
+        <v>817</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O62" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P62" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T62" s="2" t="str">
         <f>IF(ISBLANK(N62)=TRUE,"Pending","Done")</f>
@@ -7019,63 +7069,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>146</v>
+        <v>67</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>148</v>
+        <v>68</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>150</v>
+        <v>71</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="K63" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O63" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P63" s="3" t="s">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="Q63" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T63" s="2" t="str">
         <f>IF(ISBLANK(N63)=TRUE,"Pending","Done")</f>
@@ -7085,18 +7135,18 @@
         <v>499</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="105" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>148</v>
+        <v>212</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>98</v>
@@ -7105,10 +7155,10 @@
         <v>99</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>153</v>
+        <v>817</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>99</v>
@@ -7120,28 +7170,28 @@
         <v>505</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O64" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P64" s="3" t="s">
-        <v>634</v>
+        <v>649</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>727</v>
+        <v>743</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T64" s="2" t="str">
         <f>IF(ISBLANK(N64)=TRUE,"Pending","Done")</f>
@@ -7151,63 +7201,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>354</v>
+        <v>146</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>355</v>
+        <v>148</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>356</v>
+        <v>149</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>351</v>
+        <v>98</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>357</v>
+        <v>99</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>358</v>
+        <v>150</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>799</v>
+        <v>99</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>795</v>
+        <v>99</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>577</v>
+        <v>529</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O65" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P65" s="3" t="s">
-        <v>687</v>
+        <v>633</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>774</v>
+        <v>726</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T65" s="2" t="str">
         <f>IF(ISBLANK(N65)=TRUE,"Pending","Done")</f>
@@ -7217,63 +7267,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>292</v>
+        <v>151</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>293</v>
+        <v>152</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>294</v>
+        <v>148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>295</v>
+        <v>98</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>296</v>
+        <v>99</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>297</v>
+        <v>150</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>819</v>
+        <v>153</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>801</v>
+        <v>99</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>798</v>
+        <v>99</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>509</v>
+        <v>530</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>597</v>
+        <v>817</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O66" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P66" s="3" t="s">
-        <v>616</v>
+        <v>634</v>
       </c>
       <c r="Q66" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>709</v>
+        <v>727</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T66" s="2" t="str">
         <f>IF(ISBLANK(N66)=TRUE,"Pending","Done")</f>
@@ -7283,63 +7333,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="120" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>138</v>
+        <v>354</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>139</v>
+        <v>355</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>128</v>
+        <v>351</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>99</v>
+        <v>357</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>141</v>
+        <v>358</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>99</v>
+        <v>798</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>99</v>
+        <v>794</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O67" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P67" s="3" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="Q67" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>787</v>
+        <v>773</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T67" s="2" t="str">
         <f>IF(ISBLANK(N67)=TRUE,"Pending","Done")</f>
@@ -7349,129 +7399,129 @@
         <v>499</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="120" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>122</v>
+        <v>293</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>123</v>
+        <v>294</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>98</v>
+        <v>295</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>99</v>
+        <v>296</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>124</v>
+        <v>297</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>99</v>
+        <v>800</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>99</v>
+        <v>797</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O68" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P68" s="3" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="Q68" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="T68" s="2" t="str">
         <f>IF(ISBLANK(N68)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="120" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>262</v>
+        <v>138</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>263</v>
+        <v>139</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>264</v>
+        <v>140</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>265</v>
+        <v>99</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>266</v>
+        <v>141</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="K69" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>566</v>
+        <v>594</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>819</v>
+        <v>599</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O69" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P69" s="3" t="s">
-        <v>669</v>
+        <v>701</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T69" s="2" t="str">
         <f>IF(ISBLANK(N69)=TRUE,"Pending","Done")</f>
@@ -7481,63 +7531,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="120" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>569</v>
+        <v>522</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>819</v>
+        <v>601</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O70" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P70" s="3" t="s">
-        <v>672</v>
+        <v>626</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>762</v>
+        <v>719</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T70" s="2" t="str">
         <f>IF(ISBLANK(N70)=TRUE,"Pending","Done")</f>
@@ -7547,63 +7597,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="105" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>88</v>
+        <v>262</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>89</v>
+        <v>263</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>90</v>
+        <v>265</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>87</v>
+        <v>266</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>91</v>
+        <v>818</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K71" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O71" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P71" s="3" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="Q71" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T71" s="2" t="str">
         <f>IF(ISBLANK(N71)=TRUE,"Pending","Done")</f>
@@ -7613,15 +7663,15 @@
         <v>499</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>83</v>
@@ -7636,13 +7686,13 @@
         <v>87</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>505</v>
@@ -7651,7 +7701,7 @@
         <v>570</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>501</v>
@@ -7660,7 +7710,7 @@
         <v>3</v>
       </c>
       <c r="P72" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>498</v>
@@ -7669,7 +7719,7 @@
         <v>762</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T72" s="2" t="str">
         <f>IF(ISBLANK(N72)=TRUE,"Pending","Done")</f>
@@ -7681,61 +7731,61 @@
     </row>
     <row r="73" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>272</v>
+        <v>92</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>273</v>
+        <v>93</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>275</v>
+        <v>90</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>820</v>
+        <v>94</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O73" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P73" s="3" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T73" s="2" t="str">
         <f>IF(ISBLANK(N73)=TRUE,"Pending","Done")</f>
@@ -7745,63 +7795,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="195" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>277</v>
+        <v>82</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>273</v>
+        <v>84</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>85</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>275</v>
+        <v>86</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>279</v>
+        <v>818</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P74" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="Q74" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>757</v>
+        <v>762</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T74" s="2" t="str">
         <f>IF(ISBLANK(N74)=TRUE,"Pending","Done")</f>
@@ -7811,63 +7861,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>306</v>
+        <v>274</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>307</v>
+        <v>85</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>308</v>
+        <v>799</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>308</v>
+        <v>799</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>601</v>
+        <v>817</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O75" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P75" s="3" t="s">
-        <v>697</v>
+        <v>666</v>
       </c>
       <c r="Q75" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>783</v>
+        <v>757</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T75" s="2" t="str">
         <f>IF(ISBLANK(N75)=TRUE,"Pending","Done")</f>
@@ -7877,63 +7927,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="195" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>230</v>
+        <v>278</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>232</v>
+        <v>85</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>233</v>
+        <v>275</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>820</v>
+        <v>279</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O76" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P76" s="3" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="Q76" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T76" s="2" t="str">
         <f>IF(ISBLANK(N76)=TRUE,"Pending","Done")</f>
@@ -7943,63 +7993,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>491</v>
+        <v>304</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>492</v>
+        <v>305</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>493</v>
+        <v>306</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>98</v>
+        <v>307</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>494</v>
+        <v>308</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>495</v>
+        <v>309</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="K77" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>548</v>
+        <v>590</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O77" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P77" s="3" t="s">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="Q77" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T77" s="2" t="str">
         <f>IF(ISBLANK(N77)=TRUE,"Pending","Done")</f>
@@ -8009,108 +8059,108 @@
         <v>499</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>106</v>
+        <v>230</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>107</v>
+        <v>231</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>98</v>
+        <v>232</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>99</v>
+        <v>233</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>108</v>
+        <v>234</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="K78" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>547</v>
+        <v>578</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>602</v>
+        <v>817</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O78" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P78" s="3" t="s">
-        <v>650</v>
+        <v>684</v>
       </c>
       <c r="Q78" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>744</v>
+        <v>770</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T78" s="2" t="str">
         <f>IF(ISBLANK(N78)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U78" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>257</v>
+        <v>491</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>258</v>
+        <v>492</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>259</v>
+        <v>493</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>260</v>
+        <v>494</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>261</v>
+        <v>495</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>790</v>
+        <v>799</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="M79" s="3" t="s">
         <v>599</v>
@@ -8119,19 +8169,19 @@
         <v>501</v>
       </c>
       <c r="O79" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P79" s="3" t="s">
-        <v>614</v>
+        <v>651</v>
       </c>
       <c r="Q79" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>707</v>
+        <v>745</v>
       </c>
       <c r="S79" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T79" s="2" t="str">
         <f>IF(ISBLANK(N79)=TRUE,"Pending","Done")</f>
@@ -8141,129 +8191,129 @@
         <v>499</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>337</v>
+        <v>105</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>338</v>
+        <v>106</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>339</v>
+        <v>107</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>340</v>
+        <v>99</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>341</v>
+        <v>108</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="K80" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O80" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P80" s="3" t="s">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="Q80" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>760</v>
+        <v>744</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T80" s="2" t="str">
         <f>IF(ISBLANK(N80)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U80" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="81" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>99</v>
+        <v>260</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>99</v>
+        <v>789</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>543</v>
+        <v>511</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O81" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P81" s="3" t="s">
-        <v>647</v>
+        <v>614</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>740</v>
+        <v>707</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T81" s="2" t="str">
         <f>IF(ISBLANK(N81)=TRUE,"Pending","Done")</f>
@@ -8273,63 +8323,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>241</v>
+        <v>337</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>26</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>242</v>
+        <v>338</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>243</v>
+        <v>339</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>244</v>
+        <v>341</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>99</v>
+        <v>799</v>
       </c>
       <c r="K82" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O82" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P82" s="3" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="Q82" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R82" s="3" t="s">
-        <v>786</v>
+        <v>760</v>
       </c>
       <c r="S82" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T82" s="2" t="str">
         <f>IF(ISBLANK(N82)=TRUE,"Pending","Done")</f>
@@ -8339,45 +8389,45 @@
         <v>499</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>363</v>
+        <v>206</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>364</v>
+        <v>207</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>365</v>
+        <v>208</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>366</v>
+        <v>98</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>367</v>
+        <v>99</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>368</v>
+        <v>209</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>367</v>
+        <v>99</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>367</v>
+        <v>99</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>510</v>
+        <v>543</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>501</v>
@@ -8386,16 +8436,16 @@
         <v>4</v>
       </c>
       <c r="P83" s="3" t="s">
-        <v>613</v>
+        <v>647</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>706</v>
+        <v>740</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T83" s="2" t="str">
         <f>IF(ISBLANK(N83)=TRUE,"Pending","Done")</f>
@@ -8405,63 +8455,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>288</v>
+        <v>243</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>289</v>
+        <v>128</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>290</v>
+        <v>99</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>291</v>
+        <v>244</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>799</v>
+        <v>99</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>798</v>
+        <v>99</v>
       </c>
       <c r="K84" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="L84" s="3" t="s">
-        <v>577</v>
+        <v>593</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>604</v>
+        <v>817</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O84" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P84" s="3" t="s">
-        <v>682</v>
+        <v>700</v>
       </c>
       <c r="Q84" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R84" s="3" t="s">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="S84" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T84" s="2" t="str">
         <f>IF(ISBLANK(N84)=TRUE,"Pending","Done")</f>
@@ -8471,63 +8521,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="120" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>113</v>
+        <v>363</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>114</v>
+        <v>364</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>115</v>
+        <v>365</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>116</v>
+        <v>368</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O85" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P85" s="3" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="Q85" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R85" s="3" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="S85" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T85" s="2" t="str">
         <f>IF(ISBLANK(N85)=TRUE,"Pending","Done")</f>
@@ -8537,63 +8587,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>186</v>
+        <v>286</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>187</v>
+        <v>287</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>98</v>
+        <v>289</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>99</v>
+        <v>290</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>189</v>
+        <v>291</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>99</v>
+        <v>798</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>99</v>
+        <v>797</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O86" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P86" s="3" t="s">
-        <v>642</v>
+        <v>682</v>
       </c>
       <c r="Q86" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R86" s="3" t="s">
-        <v>735</v>
+        <v>768</v>
       </c>
       <c r="S86" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T86" s="2" t="str">
         <f>IF(ISBLANK(N86)=TRUE,"Pending","Done")</f>
@@ -8603,18 +8653,18 @@
         <v>499</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" ht="120" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>98</v>
@@ -8623,10 +8673,10 @@
         <v>99</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>99</v>
@@ -8638,28 +8688,28 @@
         <v>505</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="M87" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O87" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P87" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="Q87" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R87" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="S87" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="T87" s="2" t="str">
         <f>IF(ISBLANK(N87)=TRUE,"Pending","Done")</f>
@@ -8669,30 +8719,30 @@
         <v>499</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="105" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>127</v>
+        <v>188</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>129</v>
+        <v>189</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>99</v>
@@ -8704,28 +8754,28 @@
         <v>505</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O88" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P88" s="3" t="s">
-        <v>698</v>
+        <v>642</v>
       </c>
       <c r="Q88" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R88" s="3" t="s">
-        <v>784</v>
+        <v>735</v>
       </c>
       <c r="S88" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T88" s="2" t="str">
         <f>IF(ISBLANK(N88)=TRUE,"Pending","Done")</f>
@@ -8735,18 +8785,18 @@
         <v>499</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>98</v>
@@ -8755,10 +8805,10 @@
         <v>99</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>99</v>
@@ -8770,28 +8820,28 @@
         <v>505</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O89" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P89" s="3" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R89" s="3" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="S89" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T89" s="2" t="str">
         <f>IF(ISBLANK(N89)=TRUE,"Pending","Done")</f>
@@ -8801,63 +8851,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" ht="105" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>442</v>
+        <v>125</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>443</v>
+        <v>126</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>444</v>
+        <v>127</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>445</v>
+        <v>128</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>446</v>
+        <v>99</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>447</v>
+        <v>129</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="K90" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O90" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P90" s="3" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="Q90" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R90" s="3" t="s">
-        <v>765</v>
+        <v>783</v>
       </c>
       <c r="S90" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T90" s="2" t="str">
         <f>IF(ISBLANK(N90)=TRUE,"Pending","Done")</f>
@@ -8867,129 +8917,129 @@
         <v>499</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="90" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>40</v>
+        <v>168</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>43</v>
+        <v>169</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>800</v>
+        <v>817</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="K91" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K91" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L91" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="M91" s="2" t="s">
+      <c r="L91" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="M91" s="3" t="s">
         <v>602</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="O91" s="2">
+      <c r="O91" s="3">
         <v>4</v>
       </c>
-      <c r="P91" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="Q91" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="S91" s="2" t="s">
-        <v>819</v>
+      <c r="P91" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="T91" s="2" t="str">
         <f>IF(ISBLANK(N91)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
-      <c r="U91" s="2" t="s">
+      <c r="U91" s="3" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>359</v>
+        <v>442</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>360</v>
+        <v>443</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>361</v>
+        <v>444</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>289</v>
+        <v>445</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>793</v>
+        <v>446</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>362</v>
+        <v>447</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L92" s="3" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O92" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P92" s="3" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="Q92" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R92" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="S92" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T92" s="2" t="str">
         <f>IF(ISBLANK(N92)=TRUE,"Pending","Done")</f>
@@ -8999,109 +9049,111 @@
         <v>499</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>417</v>
+        <v>38</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>147</v>
+        <v>19</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D93" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E93" s="2" t="s">
-        <v>419</v>
+        <v>41</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>367</v>
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>420</v>
+        <v>43</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>367</v>
+        <v>817</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="L93" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="M93" s="3" t="s">
-        <v>601</v>
+        <v>799</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>602</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="O93" s="3">
+      <c r="O93" s="2">
         <v>4</v>
       </c>
-      <c r="P93" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="Q93" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="R93" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="S93" s="3" t="s">
-        <v>819</v>
+      <c r="P93" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q93" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="S93" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="T93" s="2" t="str">
         <f>IF(ISBLANK(N93)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
-      <c r="U93" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="94" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+      <c r="U93" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>395</v>
+        <v>359</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>396</v>
+        <v>360</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>397</v>
+        <v>361</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>98</v>
+        <v>289</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>398</v>
+        <v>792</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>399</v>
+        <v>362</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>398</v>
+        <v>799</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>398</v>
+        <v>799</v>
       </c>
       <c r="K94" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>501</v>
@@ -9110,16 +9162,16 @@
         <v>8</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>643</v>
+        <v>681</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R94" s="3" t="s">
-        <v>736</v>
+        <v>767</v>
       </c>
       <c r="S94" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T94" s="2" t="str">
         <f>IF(ISBLANK(N94)=TRUE,"Pending","Done")</f>
@@ -9129,63 +9181,61 @@
         <v>499</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>154</v>
+        <v>417</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>19</v>
+        <v>147</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>156</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="D95" s="2"/>
       <c r="E95" s="2" t="s">
-        <v>98</v>
+        <v>419</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>157</v>
+        <v>420</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="K95" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>520</v>
+        <v>581</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O95" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P95" s="3" t="s">
-        <v>624</v>
+        <v>688</v>
       </c>
       <c r="Q95" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R95" s="3" t="s">
-        <v>717</v>
+        <v>774</v>
       </c>
       <c r="S95" s="3" t="s">
-        <v>789</v>
+        <v>817</v>
       </c>
       <c r="T95" s="2" t="str">
         <f>IF(ISBLANK(N95)=TRUE,"Pending","Done")</f>
@@ -9197,40 +9247,40 @@
     </row>
     <row r="96" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>307</v>
+        <v>98</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>589</v>
+        <v>539</v>
       </c>
       <c r="M96" s="3" t="s">
         <v>602</v>
@@ -9242,16 +9292,16 @@
         <v>8</v>
       </c>
       <c r="P96" s="3" t="s">
-        <v>696</v>
+        <v>643</v>
       </c>
       <c r="Q96" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R96" s="3" t="s">
-        <v>782</v>
+        <v>736</v>
       </c>
       <c r="S96" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T96" s="2" t="str">
         <f>IF(ISBLANK(N96)=TRUE,"Pending","Done")</f>
@@ -9261,63 +9311,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>379</v>
+        <v>154</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>380</v>
+        <v>155</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>381</v>
+        <v>156</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>382</v>
+        <v>98</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>383</v>
+        <v>99</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>384</v>
+        <v>157</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>799</v>
+        <v>99</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>797</v>
+        <v>99</v>
       </c>
       <c r="K97" s="3" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O97" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P97" s="3" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="Q97" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R97" s="3" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="S97" s="3" t="s">
-        <v>819</v>
+        <v>788</v>
       </c>
       <c r="T97" s="2" t="str">
         <f>IF(ISBLANK(N97)=TRUE,"Pending","Done")</f>
@@ -9327,63 +9377,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>219</v>
+        <v>404</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>220</v>
+        <v>405</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>221</v>
+        <v>406</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>224</v>
+        <v>407</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>800</v>
+        <v>308</v>
       </c>
       <c r="K98" s="3" t="s">
         <v>505</v>
       </c>
       <c r="L98" s="3" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>819</v>
+        <v>602</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O98" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P98" s="3" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="Q98" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R98" s="3" t="s">
-        <v>776</v>
+        <v>781</v>
       </c>
       <c r="S98" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T98" s="2" t="str">
         <f>IF(ISBLANK(N98)=TRUE,"Pending","Done")</f>
@@ -9393,63 +9443,63 @@
         <v>499</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>225</v>
+        <v>379</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>226</v>
+        <v>380</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>220</v>
+        <v>381</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>222</v>
+        <v>382</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>227</v>
+        <v>383</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>224</v>
+        <v>384</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>228</v>
+        <v>817</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="L99" s="3" t="s">
-        <v>583</v>
+        <v>509</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>819</v>
+        <v>597</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>501</v>
       </c>
       <c r="O99" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P99" s="3" t="s">
-        <v>690</v>
+        <v>612</v>
       </c>
       <c r="Q99" s="3" t="s">
         <v>498</v>
       </c>
       <c r="R99" s="3" t="s">
-        <v>776</v>
+        <v>705</v>
       </c>
       <c r="S99" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="T99" s="2" t="str">
         <f>IF(ISBLANK(N99)=TRUE,"Pending","Done")</f>
@@ -9459,92 +9509,1215 @@
         <v>499</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="K100" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K100" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L100" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="M100" s="2" t="s">
-        <v>602</v>
+      <c r="L100" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="O100" s="2">
-        <v>7</v>
-      </c>
-      <c r="P100" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="Q100" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="R100" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>819</v>
+      <c r="O100" s="3">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>817</v>
       </c>
       <c r="T100" s="2" t="str">
         <f>IF(ISBLANK(N100)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
-      <c r="U100" s="2" t="s">
+      <c r="U100" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O101" s="3">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T101" s="2" t="str">
+        <f>IF(ISBLANK(N101)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O102" s="2">
+        <v>7</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="Q102" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="T102" s="2" t="str">
+        <f>IF(ISBLANK(N102)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
+      </c>
+      <c r="U102" s="2" t="s">
         <v>499</v>
       </c>
     </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C104" s="4"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C105" s="4"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C106" s="4"/>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C107" s="4"/>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C108" s="4"/>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C109" s="4"/>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C110" s="4"/>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C111" s="4"/>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="C112" s="4"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C113" s="4"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C114" s="4"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C115" s="4"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C116" s="4"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C117" s="4"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C118" s="4"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C119" s="4"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C120" s="4"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C121" s="4"/>
+    </row>
+    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C122" s="4"/>
+    </row>
+    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C123" s="4"/>
+    </row>
+    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C124" s="4"/>
+    </row>
+    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C125" s="4"/>
+    </row>
+    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C126" s="4"/>
+    </row>
+    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C127" s="4"/>
+    </row>
+    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C128" s="4"/>
+    </row>
+    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C129" s="4"/>
+    </row>
+    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C130" s="4"/>
+    </row>
+    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C131" s="4"/>
+    </row>
+    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C132" s="4"/>
+    </row>
+    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C133" s="4"/>
+    </row>
+    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C134" s="4"/>
+    </row>
+    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C135" s="4"/>
+    </row>
+    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C136" s="4"/>
+    </row>
+    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C137" s="4"/>
+    </row>
+    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C138" s="4"/>
+    </row>
+    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C139" s="4"/>
+    </row>
+    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C140" s="4"/>
+    </row>
+    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C141" s="4"/>
+    </row>
+    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C142" s="4"/>
+    </row>
+    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C143" s="4"/>
+    </row>
+    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C144" s="4"/>
+    </row>
+    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C145" s="4"/>
+    </row>
+    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C146" s="4"/>
+    </row>
+    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C147" s="4"/>
+    </row>
+    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C148" s="4"/>
+    </row>
+    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C149" s="4"/>
+    </row>
+    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C150" s="4"/>
+    </row>
+    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C151" s="4"/>
+    </row>
+    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C152" s="4"/>
+    </row>
+    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C153" s="4"/>
+    </row>
+    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C154" s="4"/>
+    </row>
+    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C155" s="4"/>
+    </row>
+    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C156" s="4"/>
+    </row>
+    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C157" s="4"/>
+    </row>
+    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C158" s="4"/>
+    </row>
+    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C159" s="4"/>
+    </row>
+    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C160" s="4"/>
+    </row>
+    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C161" s="4"/>
+    </row>
+    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C162" s="4"/>
+    </row>
+    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C163" s="4"/>
+    </row>
+    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C164" s="4"/>
+    </row>
+    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C165" s="4"/>
+    </row>
+    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C166" s="4"/>
+    </row>
+    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C167" s="4"/>
+    </row>
+    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C168" s="4"/>
+    </row>
+    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C169" s="4"/>
+    </row>
+    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C170" s="4"/>
+    </row>
+    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C171" s="4"/>
+    </row>
+    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C172" s="4"/>
+    </row>
+    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C173" s="4"/>
+    </row>
+    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C174" s="4"/>
+    </row>
+    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C175" s="4"/>
+    </row>
+    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C176" s="4"/>
+    </row>
+    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C177" s="4"/>
+    </row>
+    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C178" s="4"/>
+    </row>
+    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C179" s="4"/>
+    </row>
+    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C180" s="4"/>
+    </row>
+    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C181" s="4"/>
+    </row>
+    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C182" s="4"/>
+    </row>
+    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C183" s="4"/>
+    </row>
+    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C184" s="4"/>
+    </row>
+    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C185" s="4"/>
+    </row>
+    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C186" s="4"/>
+    </row>
+    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C187" s="4"/>
+    </row>
+    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C188" s="4"/>
+    </row>
+    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C189" s="4"/>
+    </row>
+    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C190" s="4"/>
+    </row>
+    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C191" s="4"/>
+    </row>
+    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C192" s="4"/>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C193" s="4"/>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C194" s="4"/>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C195" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U100" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U100">
-      <sortCondition descending="1" ref="O1:O100"/>
-    </sortState>
-  </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U101">
-    <sortCondition ref="G1:G101"/>
+  <autoFilter ref="A1:U102" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U195">
+    <sortCondition ref="G1:G195"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A1:U10000">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>$U1="Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D41" r:id="rId1" xr:uid="{6A5052EB-107D-4E27-B5E6-CA44C24A63E1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85BC12BB-902C-4E6A-B1CA-569154A1AAFC}">
+  <dimension ref="A1:U10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" customWidth="1"/>
+    <col min="4" max="4" width="40.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="66.42578125" customWidth="1"/>
+    <col min="8" max="8" width="57.85546875" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.85546875" customWidth="1"/>
+    <col min="16" max="16" width="50.5703125" customWidth="1"/>
+    <col min="17" max="17" width="16.28515625" customWidth="1"/>
+    <col min="18" max="18" width="48.7109375" customWidth="1"/>
+    <col min="19" max="19" width="17.5703125" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O2" s="3">
+        <v>5</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T2" s="2" t="str">
+        <f t="shared" ref="T2:T10" si="0">IF(ISBLANK(N2)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O3" s="3">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T3" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O4" s="3">
+        <v>5</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O5" s="3">
+        <v>2</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O6" s="3">
+        <v>5</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O7" s="3">
+        <v>3</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O8" s="2">
+        <v>4</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="T8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O9" s="3">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="O10" s="3">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="T10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Done</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:U10">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$U1="Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C10">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:G10">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1:O10">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9556,12 +10729,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$U1="Yes"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/2-master_reddit_links_curated.xlsx
+++ b/data/2-master_reddit_links_curated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\RedditBoardApplication\RedditBoardV3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EA6F10-E8C3-4DE5-A196-3B33E23BBEFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2820C887-A236-4A8F-B53D-2374C8CB8543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="238" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="833">
   <si>
     <t>reddit_id</t>
   </si>
@@ -2536,6 +2536,9 @@
   </si>
   <si>
     <t>nq39etcczr2g1.gif</t>
+  </si>
+  <si>
+    <t>mp4m9l7</t>
   </si>
 </sst>
 </file>
@@ -2637,7 +2640,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FFFF00FF"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF00FF"/>
@@ -3110,7 +3118,7 @@
         <v>788</v>
       </c>
       <c r="T2" s="2" t="str">
-        <f>IF(ISBLANK(N2)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="T2:T33" si="0">IF(ISBLANK(N2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U2" s="3" t="s">
@@ -3176,7 +3184,7 @@
         <v>788</v>
       </c>
       <c r="T3" s="2" t="str">
-        <f>IF(ISBLANK(N3)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U3" s="3" t="s">
@@ -3242,7 +3250,7 @@
         <v>788</v>
       </c>
       <c r="T4" s="2" t="str">
-        <f>IF(ISBLANK(N4)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U4" s="3" t="s">
@@ -3308,7 +3316,7 @@
         <v>817</v>
       </c>
       <c r="T5" s="2" t="str">
-        <f>IF(ISBLANK(N5)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U5" s="3" t="s">
@@ -3374,7 +3382,7 @@
         <v>788</v>
       </c>
       <c r="T6" s="2" t="str">
-        <f>IF(ISBLANK(N6)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U6" s="3" t="s">
@@ -3440,7 +3448,7 @@
         <v>817</v>
       </c>
       <c r="T7" s="2" t="str">
-        <f>IF(ISBLANK(N7)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U7" s="3" t="s">
@@ -3506,7 +3514,7 @@
         <v>817</v>
       </c>
       <c r="T8" s="2" t="str">
-        <f>IF(ISBLANK(N8)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U8" s="3" t="s">
@@ -3572,7 +3580,7 @@
         <v>817</v>
       </c>
       <c r="T9" s="2" t="str">
-        <f>IF(ISBLANK(N9)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U9" s="3" t="s">
@@ -3636,7 +3644,7 @@
         <v>817</v>
       </c>
       <c r="T10" s="2" t="str">
-        <f>IF(ISBLANK(N10)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U10" s="3" t="s">
@@ -3702,7 +3710,7 @@
         <v>817</v>
       </c>
       <c r="T11" s="2" t="str">
-        <f>IF(ISBLANK(N11)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U11" s="3" t="s">
@@ -3768,7 +3776,7 @@
         <v>788</v>
       </c>
       <c r="T12" s="2" t="str">
-        <f>IF(ISBLANK(N12)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U12" s="3" t="s">
@@ -3834,7 +3842,7 @@
         <v>817</v>
       </c>
       <c r="T13" s="2" t="str">
-        <f>IF(ISBLANK(N13)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U13" s="3" t="s">
@@ -3900,7 +3908,7 @@
         <v>817</v>
       </c>
       <c r="T14" s="2" t="str">
-        <f>IF(ISBLANK(N14)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U14" s="2" t="s">
@@ -3966,7 +3974,7 @@
         <v>788</v>
       </c>
       <c r="T15" s="2" t="str">
-        <f>IF(ISBLANK(N15)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U15" s="3" t="s">
@@ -4032,7 +4040,7 @@
         <v>817</v>
       </c>
       <c r="T16" s="2" t="str">
-        <f>IF(ISBLANK(N16)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U16" s="2" t="s">
@@ -4098,7 +4106,7 @@
         <v>817</v>
       </c>
       <c r="T17" s="2" t="str">
-        <f>IF(ISBLANK(N17)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U17" s="2" t="s">
@@ -4164,7 +4172,7 @@
         <v>817</v>
       </c>
       <c r="T18" s="2" t="str">
-        <f>IF(ISBLANK(N18)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U18" s="3" t="s">
@@ -4230,7 +4238,7 @@
         <v>817</v>
       </c>
       <c r="T19" s="2" t="str">
-        <f>IF(ISBLANK(N19)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U19" s="3" t="s">
@@ -4296,7 +4304,7 @@
         <v>817</v>
       </c>
       <c r="T20" s="2" t="str">
-        <f>IF(ISBLANK(N20)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U20" s="3" t="s">
@@ -4362,7 +4370,7 @@
         <v>817</v>
       </c>
       <c r="T21" s="2" t="str">
-        <f>IF(ISBLANK(N21)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U21" s="3" t="s">
@@ -4428,7 +4436,7 @@
         <v>817</v>
       </c>
       <c r="T22" s="2" t="str">
-        <f>IF(ISBLANK(N22)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U22" s="3" t="s">
@@ -4492,7 +4500,7 @@
         <v>817</v>
       </c>
       <c r="T23" s="2" t="str">
-        <f>IF(ISBLANK(N23)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U23" s="3" t="s">
@@ -4558,7 +4566,7 @@
         <v>817</v>
       </c>
       <c r="T24" s="2" t="str">
-        <f>IF(ISBLANK(N24)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U24" s="3" t="s">
@@ -4624,7 +4632,7 @@
         <v>817</v>
       </c>
       <c r="T25" s="2" t="str">
-        <f>IF(ISBLANK(N25)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U25" s="3" t="s">
@@ -4690,7 +4698,7 @@
         <v>817</v>
       </c>
       <c r="T26" s="2" t="str">
-        <f>IF(ISBLANK(N26)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U26" s="3" t="s">
@@ -4756,7 +4764,7 @@
         <v>817</v>
       </c>
       <c r="T27" s="2" t="str">
-        <f>IF(ISBLANK(N27)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U27" s="3" t="s">
@@ -4822,7 +4830,7 @@
         <v>817</v>
       </c>
       <c r="T28" s="2" t="str">
-        <f>IF(ISBLANK(N28)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U28" s="3" t="s">
@@ -4888,7 +4896,7 @@
         <v>817</v>
       </c>
       <c r="T29" s="2" t="str">
-        <f>IF(ISBLANK(N29)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U29" s="3" t="s">
@@ -4954,7 +4962,7 @@
         <v>817</v>
       </c>
       <c r="T30" s="2" t="str">
-        <f>IF(ISBLANK(N30)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U30" s="3" t="s">
@@ -5020,7 +5028,7 @@
         <v>817</v>
       </c>
       <c r="T31" s="2" t="str">
-        <f>IF(ISBLANK(N31)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U31" s="3" t="s">
@@ -5086,7 +5094,7 @@
         <v>817</v>
       </c>
       <c r="T32" s="2" t="str">
-        <f>IF(ISBLANK(N32)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U32" s="3" t="s">
@@ -5152,7 +5160,7 @@
         <v>817</v>
       </c>
       <c r="T33" s="2" t="str">
-        <f>IF(ISBLANK(N33)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="U33" s="3" t="s">
@@ -5218,7 +5226,7 @@
         <v>817</v>
       </c>
       <c r="T34" s="2" t="str">
-        <f>IF(ISBLANK(N34)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="T34:T65" si="1">IF(ISBLANK(N34)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U34" s="3" t="s">
@@ -5284,7 +5292,7 @@
         <v>817</v>
       </c>
       <c r="T35" s="2" t="str">
-        <f>IF(ISBLANK(N35)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U35" s="3" t="s">
@@ -5350,7 +5358,7 @@
         <v>817</v>
       </c>
       <c r="T36" s="2" t="str">
-        <f>IF(ISBLANK(N36)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U36" s="3" t="s">
@@ -5416,7 +5424,7 @@
         <v>817</v>
       </c>
       <c r="T37" s="2" t="str">
-        <f>IF(ISBLANK(N37)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U37" s="3" t="s">
@@ -5482,7 +5490,7 @@
         <v>817</v>
       </c>
       <c r="T38" s="2" t="str">
-        <f>IF(ISBLANK(N38)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U38" s="3" t="s">
@@ -5548,7 +5556,7 @@
         <v>788</v>
       </c>
       <c r="T39" s="2" t="str">
-        <f>IF(ISBLANK(N39)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U39" s="3" t="s">
@@ -5614,7 +5622,7 @@
         <v>788</v>
       </c>
       <c r="T40" s="2" t="str">
-        <f>IF(ISBLANK(N40)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U40" s="3" t="s">
@@ -5622,7 +5630,9 @@
       </c>
     </row>
     <row r="41" spans="1:21" ht="60" x14ac:dyDescent="0.25">
-      <c r="A41" s="2"/>
+      <c r="A41" s="2" t="s">
+        <v>832</v>
+      </c>
       <c r="B41" s="2" t="s">
         <v>79</v>
       </c>
@@ -5678,7 +5688,7 @@
         <v>817</v>
       </c>
       <c r="T41" s="2" t="str">
-        <f>IF(ISBLANK(N41)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U41" s="3" t="s">
@@ -5744,7 +5754,7 @@
         <v>788</v>
       </c>
       <c r="T42" s="2" t="str">
-        <f>IF(ISBLANK(N42)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U42" s="3" t="s">
@@ -5810,7 +5820,7 @@
         <v>817</v>
       </c>
       <c r="T43" s="2" t="str">
-        <f>IF(ISBLANK(N43)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U43" s="3" t="s">
@@ -5876,7 +5886,7 @@
         <v>817</v>
       </c>
       <c r="T44" s="2" t="str">
-        <f>IF(ISBLANK(N44)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U44" s="3" t="s">
@@ -5942,7 +5952,7 @@
         <v>817</v>
       </c>
       <c r="T45" s="2" t="str">
-        <f>IF(ISBLANK(N45)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U45" s="3" t="s">
@@ -6008,7 +6018,7 @@
         <v>817</v>
       </c>
       <c r="T46" s="2" t="str">
-        <f>IF(ISBLANK(N46)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U46" s="3" t="s">
@@ -6074,7 +6084,7 @@
         <v>817</v>
       </c>
       <c r="T47" s="2" t="str">
-        <f>IF(ISBLANK(N47)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U47" s="2" t="s">
@@ -6140,7 +6150,7 @@
         <v>817</v>
       </c>
       <c r="T48" s="2" t="str">
-        <f>IF(ISBLANK(N48)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U48" s="3" t="s">
@@ -6206,7 +6216,7 @@
         <v>817</v>
       </c>
       <c r="T49" s="2" t="str">
-        <f>IF(ISBLANK(N49)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U49" s="3" t="s">
@@ -6272,7 +6282,7 @@
         <v>817</v>
       </c>
       <c r="T50" s="2" t="str">
-        <f>IF(ISBLANK(N50)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U50" s="3" t="s">
@@ -6338,7 +6348,7 @@
         <v>817</v>
       </c>
       <c r="T51" s="2" t="str">
-        <f>IF(ISBLANK(N51)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U51" s="3" t="s">
@@ -6404,7 +6414,7 @@
         <v>788</v>
       </c>
       <c r="T52" s="2" t="str">
-        <f>IF(ISBLANK(N52)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U52" s="3" t="s">
@@ -6470,7 +6480,7 @@
         <v>817</v>
       </c>
       <c r="T53" s="2" t="str">
-        <f>IF(ISBLANK(N53)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U53" s="3" t="s">
@@ -6536,7 +6546,7 @@
         <v>817</v>
       </c>
       <c r="T54" s="2" t="str">
-        <f>IF(ISBLANK(N54)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U54" s="3" t="s">
@@ -6600,7 +6610,7 @@
         <v>817</v>
       </c>
       <c r="T55" s="2" t="str">
-        <f>IF(ISBLANK(N55)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U55" s="3" t="s">
@@ -6666,7 +6676,7 @@
         <v>788</v>
       </c>
       <c r="T56" s="2" t="str">
-        <f>IF(ISBLANK(N56)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U56" s="3" t="s">
@@ -6732,7 +6742,7 @@
         <v>817</v>
       </c>
       <c r="T57" s="2" t="str">
-        <f>IF(ISBLANK(N57)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U57" s="3" t="s">
@@ -6798,7 +6808,7 @@
         <v>817</v>
       </c>
       <c r="T58" s="2" t="str">
-        <f>IF(ISBLANK(N58)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U58" s="3" t="s">
@@ -6864,7 +6874,7 @@
         <v>788</v>
       </c>
       <c r="T59" s="2" t="str">
-        <f>IF(ISBLANK(N59)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U59" s="3" t="s">
@@ -6930,7 +6940,7 @@
         <v>817</v>
       </c>
       <c r="T60" s="2" t="str">
-        <f>IF(ISBLANK(N60)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U60" s="3" t="s">
@@ -6996,7 +7006,7 @@
         <v>817</v>
       </c>
       <c r="T61" s="2" t="str">
-        <f>IF(ISBLANK(N61)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U61" s="3" t="s">
@@ -7062,7 +7072,7 @@
         <v>817</v>
       </c>
       <c r="T62" s="2" t="str">
-        <f>IF(ISBLANK(N62)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U62" s="3" t="s">
@@ -7128,7 +7138,7 @@
         <v>817</v>
       </c>
       <c r="T63" s="2" t="str">
-        <f>IF(ISBLANK(N63)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U63" s="3" t="s">
@@ -7194,7 +7204,7 @@
         <v>817</v>
       </c>
       <c r="T64" s="2" t="str">
-        <f>IF(ISBLANK(N64)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U64" s="3" t="s">
@@ -7260,7 +7270,7 @@
         <v>817</v>
       </c>
       <c r="T65" s="2" t="str">
-        <f>IF(ISBLANK(N65)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="U65" s="3" t="s">
@@ -7326,7 +7336,7 @@
         <v>817</v>
       </c>
       <c r="T66" s="2" t="str">
-        <f>IF(ISBLANK(N66)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="T66:T102" si="2">IF(ISBLANK(N66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="U66" s="3" t="s">
@@ -7392,7 +7402,7 @@
         <v>788</v>
       </c>
       <c r="T67" s="2" t="str">
-        <f>IF(ISBLANK(N67)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U67" s="3" t="s">
@@ -7458,7 +7468,7 @@
         <v>817</v>
       </c>
       <c r="T68" s="2" t="str">
-        <f>IF(ISBLANK(N68)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U68" s="3" t="s">
@@ -7524,7 +7534,7 @@
         <v>817</v>
       </c>
       <c r="T69" s="2" t="str">
-        <f>IF(ISBLANK(N69)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U69" s="3" t="s">
@@ -7590,7 +7600,7 @@
         <v>788</v>
       </c>
       <c r="T70" s="2" t="str">
-        <f>IF(ISBLANK(N70)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U70" s="3" t="s">
@@ -7656,7 +7666,7 @@
         <v>817</v>
       </c>
       <c r="T71" s="2" t="str">
-        <f>IF(ISBLANK(N71)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U71" s="3" t="s">
@@ -7722,7 +7732,7 @@
         <v>817</v>
       </c>
       <c r="T72" s="2" t="str">
-        <f>IF(ISBLANK(N72)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U72" s="3" t="s">
@@ -7788,7 +7798,7 @@
         <v>817</v>
       </c>
       <c r="T73" s="2" t="str">
-        <f>IF(ISBLANK(N73)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U73" s="3" t="s">
@@ -7854,7 +7864,7 @@
         <v>817</v>
       </c>
       <c r="T74" s="2" t="str">
-        <f>IF(ISBLANK(N74)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U74" s="3" t="s">
@@ -7920,7 +7930,7 @@
         <v>817</v>
       </c>
       <c r="T75" s="2" t="str">
-        <f>IF(ISBLANK(N75)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U75" s="3" t="s">
@@ -7986,7 +7996,7 @@
         <v>817</v>
       </c>
       <c r="T76" s="2" t="str">
-        <f>IF(ISBLANK(N76)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U76" s="3" t="s">
@@ -8052,7 +8062,7 @@
         <v>817</v>
       </c>
       <c r="T77" s="2" t="str">
-        <f>IF(ISBLANK(N77)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U77" s="3" t="s">
@@ -8118,7 +8128,7 @@
         <v>817</v>
       </c>
       <c r="T78" s="2" t="str">
-        <f>IF(ISBLANK(N78)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U78" s="3" t="s">
@@ -8184,7 +8194,7 @@
         <v>788</v>
       </c>
       <c r="T79" s="2" t="str">
-        <f>IF(ISBLANK(N79)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U79" s="3" t="s">
@@ -8250,7 +8260,7 @@
         <v>817</v>
       </c>
       <c r="T80" s="2" t="str">
-        <f>IF(ISBLANK(N80)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U80" s="3" t="s">
@@ -8316,7 +8326,7 @@
         <v>817</v>
       </c>
       <c r="T81" s="2" t="str">
-        <f>IF(ISBLANK(N81)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U81" s="3" t="s">
@@ -8382,7 +8392,7 @@
         <v>817</v>
       </c>
       <c r="T82" s="2" t="str">
-        <f>IF(ISBLANK(N82)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U82" s="3" t="s">
@@ -8448,7 +8458,7 @@
         <v>817</v>
       </c>
       <c r="T83" s="2" t="str">
-        <f>IF(ISBLANK(N83)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U83" s="3" t="s">
@@ -8514,7 +8524,7 @@
         <v>817</v>
       </c>
       <c r="T84" s="2" t="str">
-        <f>IF(ISBLANK(N84)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U84" s="3" t="s">
@@ -8580,7 +8590,7 @@
         <v>817</v>
       </c>
       <c r="T85" s="2" t="str">
-        <f>IF(ISBLANK(N85)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U85" s="3" t="s">
@@ -8646,7 +8656,7 @@
         <v>817</v>
       </c>
       <c r="T86" s="2" t="str">
-        <f>IF(ISBLANK(N86)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U86" s="3" t="s">
@@ -8712,7 +8722,7 @@
         <v>817</v>
       </c>
       <c r="T87" s="2" t="str">
-        <f>IF(ISBLANK(N87)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U87" s="3" t="s">
@@ -8778,7 +8788,7 @@
         <v>817</v>
       </c>
       <c r="T88" s="2" t="str">
-        <f>IF(ISBLANK(N88)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U88" s="3" t="s">
@@ -8844,7 +8854,7 @@
         <v>788</v>
       </c>
       <c r="T89" s="2" t="str">
-        <f>IF(ISBLANK(N89)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U89" s="3" t="s">
@@ -8910,7 +8920,7 @@
         <v>817</v>
       </c>
       <c r="T90" s="2" t="str">
-        <f>IF(ISBLANK(N90)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U90" s="3" t="s">
@@ -8976,7 +8986,7 @@
         <v>817</v>
       </c>
       <c r="T91" s="2" t="str">
-        <f>IF(ISBLANK(N91)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U91" s="3" t="s">
@@ -9042,7 +9052,7 @@
         <v>817</v>
       </c>
       <c r="T92" s="2" t="str">
-        <f>IF(ISBLANK(N92)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U92" s="3" t="s">
@@ -9108,7 +9118,7 @@
         <v>817</v>
       </c>
       <c r="T93" s="2" t="str">
-        <f>IF(ISBLANK(N93)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U93" s="2" t="s">
@@ -9174,7 +9184,7 @@
         <v>817</v>
       </c>
       <c r="T94" s="2" t="str">
-        <f>IF(ISBLANK(N94)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U94" s="3" t="s">
@@ -9238,7 +9248,7 @@
         <v>817</v>
       </c>
       <c r="T95" s="2" t="str">
-        <f>IF(ISBLANK(N95)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U95" s="3" t="s">
@@ -9304,7 +9314,7 @@
         <v>817</v>
       </c>
       <c r="T96" s="2" t="str">
-        <f>IF(ISBLANK(N96)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U96" s="3" t="s">
@@ -9370,7 +9380,7 @@
         <v>788</v>
       </c>
       <c r="T97" s="2" t="str">
-        <f>IF(ISBLANK(N97)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U97" s="3" t="s">
@@ -9436,7 +9446,7 @@
         <v>817</v>
       </c>
       <c r="T98" s="2" t="str">
-        <f>IF(ISBLANK(N98)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U98" s="3" t="s">
@@ -9502,7 +9512,7 @@
         <v>817</v>
       </c>
       <c r="T99" s="2" t="str">
-        <f>IF(ISBLANK(N99)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U99" s="3" t="s">
@@ -9568,7 +9578,7 @@
         <v>817</v>
       </c>
       <c r="T100" s="2" t="str">
-        <f>IF(ISBLANK(N100)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U100" s="3" t="s">
@@ -9634,7 +9644,7 @@
         <v>817</v>
       </c>
       <c r="T101" s="2" t="str">
-        <f>IF(ISBLANK(N101)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U101" s="3" t="s">
@@ -9700,7 +9710,7 @@
         <v>817</v>
       </c>
       <c r="T102" s="2" t="str">
-        <f>IF(ISBLANK(N102)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="U102" s="2" t="s">
@@ -9990,18 +10000,18 @@
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="A1:U10000">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>$U1="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O1048576">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10012,11 +10022,15 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B41:B42">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D41" r:id="rId1" xr:uid="{6A5052EB-107D-4E27-B5E6-CA44C24A63E1}"/>
+    <hyperlink ref="C41" r:id="rId2" xr:uid="{5081A0D1-9E90-496A-9A6C-BD16A8C43D9C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -10707,15 +10721,15 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U10">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>$U1="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C10">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:G10">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:O10">
     <cfRule type="colorScale" priority="3">
